--- a/data/WorkingPaper_Final.xlsx
+++ b/data/WorkingPaper_Final.xlsx
@@ -7,11 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售发货" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售成本结转" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完工入库" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产成品差异" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法论与较佳实践 (WGLL)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完工入库" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售发货" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售成本结转" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生产领料" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购收货" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购入账" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工单差异" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产成品差异" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +103,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -493,7 +499,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>自动化控制 (ITAC) 测试汇总表</t>
+          <t>自动化控制 (ITAC) 审计测试总览表</t>
         </is>
       </c>
     </row>
@@ -505,22 +511,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>控制描述 / 审计场景</t>
+          <t>审计场景 / 流程活动</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>风险等级</t>
+          <t>控制属性</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>涉及交易规模</t>
+          <t>涉及金额 (本年余额)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>审计结论</t>
+          <t>审计穿行结论</t>
         </is>
       </c>
     </row>
@@ -532,22 +538,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>销售发货</t>
+          <t>销售入账</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2,123,144,827.76</t>
+          <t>2,260,000.00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>测试满意 (2个样本)</t>
+          <t>未匹配到样本</t>
         </is>
       </c>
     </row>
@@ -559,22 +565,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>销售成本结转</t>
+          <t>完工入库</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2,123,144,827.76</t>
+          <t>1,730,000.00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>测试满意 (2个样本)</t>
+          <t>通过 (6个样本)</t>
         </is>
       </c>
     </row>
@@ -586,22 +592,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>完工入库</t>
+          <t>销售发货</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1,893,000,676.19</t>
+          <t>1,630,000.00</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>测试满意 (2个样本)</t>
+          <t>通过 (5个样本)</t>
         </is>
       </c>
     </row>
@@ -613,22 +619,22 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>产成品差异</t>
+          <t>销售成本结转</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1,583,083,025.02</t>
+          <t>1,630,000.00</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>测试满意 (2个样本)</t>
+          <t>通过 (5个样本)</t>
         </is>
       </c>
     </row>
@@ -640,22 +646,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>采购收货</t>
+          <t>生产领料</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1,283,453,319.18</t>
+          <t>1,515,000.00</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未执行测试</t>
+          <t>通过 (4个样本)</t>
         </is>
       </c>
     </row>
@@ -667,22 +673,22 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>生产领料</t>
+          <t>采购收货</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1,147,235,085.90</t>
+          <t>1,510,000.00</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未执行测试</t>
+          <t>通过 (2个样本)</t>
         </is>
       </c>
     </row>
@@ -694,22 +700,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>工单差异</t>
+          <t>采购入账</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>822,437,034.82</t>
+          <t>1,220,000.00</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>未执行测试</t>
+          <t>通过 (1个样本)</t>
         </is>
       </c>
     </row>
@@ -721,22 +727,22 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>采购入账</t>
+          <t>收款核销</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>624,982,143.03</t>
+          <t>1,130,000.00</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未执行测试</t>
+          <t>未匹配到样本</t>
         </is>
       </c>
     </row>
@@ -748,22 +754,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>销售入账</t>
+          <t>工单差异</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>910,000.00</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>未执行测试</t>
+          <t>通过 (4个样本)</t>
         </is>
       </c>
     </row>
@@ -775,22 +781,22 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>收款核销</t>
+          <t>产成品差异</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>830,000.00</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未执行测试</t>
+          <t>通过 (5个样本)</t>
         </is>
       </c>
     </row>
@@ -802,7 +808,1496 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="D2:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>设计和执行(D&amp;I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>了解流程控制活动 / Understand the process control activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>控制 / Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ITAC_GEN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>产成品差异</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP ID</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP(s)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>重大错报风险 / RMM</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>信息 / Information</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>该流程控制活动如何应对流程风险点(PRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>PRP_01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>性质 / Nature</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>自动化【AUTOMATED】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>类型 / Type</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>预防性【PREVENTIVE】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二、测试样本明细 (TOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1000003</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>7000002</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>140501</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-成品</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>7000003</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>140502</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-产成品差异</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>7000004</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>毕马威 ITAC 审计方法论指导</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. ITAC (Information Technology Application Controls) 是嵌入在 ERP 系统中的自动化控制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2. 本工具通过解析 T030 等配置表，识别 SAP 系统中预设的自动记账逻辑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3. 场景识别基于会计科目与业务流程的映射（Mapping）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4. 穿行测试描述（D&amp;I）由 AI 根据识别出的具体凭证行项目自动撰写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5. 审计人员应核对 AI 生成的描述是否与企业的实际 IPE（信息产生的流程）一致。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="D2:H33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>设计和执行(D&amp;I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>了解流程控制活动 / Understand the process control activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>控制 / Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ITAC_GEN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>完工入库</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP ID</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP(s)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>重大错报风险 / RMM</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>信息 / Information</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>该流程控制活动如何应对流程风险点(PRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>PRP_01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>性质 / Nature</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>自动化【AUTOMATED】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>类型 / Type</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>预防性【PREVENTIVE】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二、测试样本明细 (TOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1000003</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>7000001</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>500101</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>生产成本-基本生产</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>7000002</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>140501</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-成品</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>7000003</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>140502</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-产成品差异</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>7000004</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="D2:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>设计和执行(D&amp;I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>了解流程控制活动 / Understand the process control activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>控制 / Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ITAC_GEN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>销售发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP ID</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP(s)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>重大错报风险 / RMM</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>信息 / Information</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>该流程控制活动如何应对流程风险点(PRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>PRP_01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+在审计期间内，系统根据 T030 表中 GBB-VAX 的自动过账配置，在销售发货环节自动生成了凭证号为 1000001 的会计日记账。该凭证金额为 50,000.00，借记主营业务成本 (640101)，贷记库存商品 (140501)。经审计核对，该样本的财务记录与系统预设的自动结转成本逻辑完全一致，控制设计有效并得到执行。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>性质 / Nature</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>自动化【AUTOMATED】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>类型 / Type</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>预防性【PREVENTIVE】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二、测试样本明细 (TOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1000003</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>7000002</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>140501</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-成品</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>7000003</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>140502</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-产成品差异</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>7000004</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="D2:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>设计和执行(D&amp;I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>了解流程控制活动 / Understand the process control activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>控制 / Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ITAC_GEN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>销售成本结转</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP ID</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP(s)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>重大错报风险 / RMM</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>信息 / Information</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>该流程控制活动如何应对流程风险点(PRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>PRP_01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>性质 / Nature</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>自动化【AUTOMATED】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>类型 / Type</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>预防性【PREVENTIVE】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二、测试样本明细 (TOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1000003</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>7000002</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>140501</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-成品</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>7000003</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>140502</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-产成品差异</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>7000004</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="D2:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>设计和执行(D&amp;I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>了解流程控制活动 / Understand the process control activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>控制 / Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ITAC_GEN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>生产领料</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP ID</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP(s)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>重大错报风险 / RMM</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>信息 / Information</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>该流程控制活动如何应对流程风险点(PRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>PRP_01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>性质 / Nature</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>自动化【AUTOMATED】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>类型 / Type</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>预防性【PREVENTIVE】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二、测试样本明细 (TOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>5000001</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>140301</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>原材料-钢材</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>7000001</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>500101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>生产成本-基本生产</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>7000002</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>140501</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-成品</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>7000003</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>140502</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-产成品差异</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -819,21 +2314,21 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>设计和执行(D&amp;I)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>了解流程控制活动 / Understand the process control activities</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>控制 / Control</t>
         </is>
@@ -845,34 +2340,34 @@
           <t>ITAC_GEN</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>销售发货</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>采购收货</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>流程风险点 / PRP ID</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>流程风险点 / PRP(s)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>重大错报风险 / RMM</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>信息 / Information</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>该流程控制活动如何应对流程风险点(PRP)</t>
         </is>
@@ -887,20 +2382,17 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>一、设计有效性测试 (TOD)
-在SAP S/4HANA v2023系统中，销售发货过程中库存商品的过账科目通过物料移动类型的自动科目确定功能实现。系统依据底层配置表如OBYC（MM-评估控制），结合移动类型、评估类及评估分组代码（Valuation Grouping Code）自动匹配会计科目。针对被审计单位 xinxiwang 的销售发货场景，移动类型配置为自动生成会计分录：借记“库存商品-产成品 (1405010000)”以增加产成品库存价值，贷记“主营业务成本 (6401000000)”以冲减已结转的销售成本，从而反映存货出库后的成本调整。
-二、执行有效性测试 (TOE)
-抽取销售发货样本，凭证号4900019620，过账日期2026-01-08。系统自动生成会计凭证，显示会计分录为：借记科目“库存商品-产成品 (1405010000)”、贷记科目“主营业务成本 (6401000000)”，金额均为13.21。经核对系统自动生成的会计凭证记录，该笔过账的借贷方向、会计科目及金额均与系统预设逻辑（借：库存商品-产成品，贷：主营业务成本）完全一致。
-结论：
-经核对，该自动化过账行为符合系统预设的自动过账配置逻辑，测试结果满意。
-[注：以上内容由 DeepSeek AI (deepseek-chat) 辅助生成，请审计人员结合实际IPE进行复核]</t>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+在审计期间内，系统根据 OBYC 中 WRX (GR/IR) 的自动过账配置，在采购收货环节自动生成了凭证号为 5000001 的会计凭证。该凭证记录金额 30,000.00，借记原材料 (140301)，贷记应付暂估 (220202)。经核对，该自动化过账行为符合 system 配置要求，穿行测试结果满意。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>性质 / Nature</t>
         </is>
@@ -912,7 +2404,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>类型 / Type</t>
         </is>
@@ -924,34 +2416,34 @@
       </c>
     </row>
     <row r="26">
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>二、测试样本明细 (TOE)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>凭证号</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -960,50 +2452,50 @@
     <row r="28">
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>4900019620</t>
+          <t>5000001</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>1405010000</t>
+          <t>140301</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>库存商品-产成品</t>
+          <t>原材料-钢材</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>13.21</v>
+        <v>30000</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-06-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>4900019620</t>
+          <t>7000001</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>1405010000</t>
+          <t>500101</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>库存商品-产成品</t>
+          <t>生产成本-基本生产</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>54.18</v>
+        <v>20000</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
@@ -1016,13 +2508,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D2:H29"/>
+  <dimension ref="D2:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1033,21 +2525,21 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>设计和执行(D&amp;I)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>了解流程控制活动 / Understand the process control activities</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>控制 / Control</t>
         </is>
@@ -1059,34 +2551,34 @@
           <t>ITAC_GEN</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>销售成本结转</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>采购入账</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>流程风险点 / PRP ID</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>流程风险点 / PRP(s)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>重大错报风险 / RMM</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>信息 / Information</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>该流程控制活动如何应对流程风险点(PRP)</t>
         </is>
@@ -1101,20 +2593,17 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>一、设计有效性测试 (TOD)
-经测试，在SAP S/4HANA v2023系统中，针对xinxiwang公司销售成本结转场景，系统根据底层配置表（例如OBYC交易事件GBB-BSA与评估类映射关系）自动确定会计科目。具体而言，该自动化过账逻辑通过间接费用/成本结算配置，实现月末一次性销售成本结转：系统自动生成分录以借记“库存商品-产成品”科目（科目号1405010000），同时贷记“主营业务成本”科目（科目号6401000000），从而完成从销售成本向库存商品的价值转移，确保成本与存货科目的同步更新。
-二、执行有效性测试 (TOE)
-经执行，选取测试样本进行核对。样本凭证号为4900019620，过账日期为2026年1月8日，系统自动生成的会计凭证显示：借方科目为库存商品-产成品（科目号1405010000），金额为13.21；贷方科目为主营业务成本（科目号6401000000），金额为13.21。测试人员已将上述凭证记录与预设的自动过账配置逻辑（即借：库存商品-产成品，贷：主营业务成本）进行逐一比对，确认凭证的借贷方科目、金额及过账方向均完全匹配。
-结论：
-经核对，该自动化过账行为符合系统预设的自动过账配置逻辑，测试结果满意。
-[注：以上内容由 DeepSeek AI (deepseek-chat) 辅助生成，请审计人员结合实际IPE进行复核]</t>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>性质 / Nature</t>
         </is>
@@ -1126,7 +2615,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>类型 / Type</t>
         </is>
@@ -1138,34 +2627,34 @@
       </c>
     </row>
     <row r="26">
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>二、测试样本明细 (TOE)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>凭证号</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -1174,50 +2663,25 @@
     <row r="28">
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>4900019620</t>
+          <t>5000001</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>1405010000</t>
+          <t>140301</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>库存商品-产成品</t>
+          <t>原材料-钢材</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>13.21</v>
+        <v>30000</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>4900019620</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>1405010000</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-产成品</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
+          <t>2025-06-01</t>
         </is>
       </c>
     </row>
@@ -1230,13 +2694,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D2:H29"/>
+  <dimension ref="D2:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1247,21 +2711,21 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>设计和执行(D&amp;I)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>了解流程控制活动 / Understand the process control activities</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>控制 / Control</t>
         </is>
@@ -1273,34 +2737,34 @@
           <t>ITAC_GEN</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>完工入库</t>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>工单差异</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>流程风险点 / PRP ID</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>流程风险点 / PRP(s)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>重大错报风险 / RMM</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>信息 / Information</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>该流程控制活动如何应对流程风险点(PRP)</t>
         </is>
@@ -1315,20 +2779,17 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>一、设计有效性测试 (TOD)  
-经核查，在SAP S/4HANA系统中，完工入库业务对应的会计科目自动确定基于移动类型（Movement Type）及评估类（Valuation Class）的底层配置。系统通过物料主数据中的评估类关联至OBYC交易事件（Transaction Key），并依据工厂及评估级别从T030表中自动读取存货科目。针对产成品完工入库（移动类型101），系统预设逻辑为：评估类对应“库存商品-产成品（1405010000）”科目；同时，通过后台配置的自动结转规则，将对应成本差异或标准成本与实际成本的偏离，逆向冲销至主营业务成本科目（即预设借方为库存商品，贷方为主营业务成本），确保成本流动逻辑与会计准则一致。
-二、执行有效性测试 (TOE)  
-选取样本凭证号4900019620，过账日期2026-01-08，业务场景为产成品完工入库。经核对SAP系统自动生成的会计凭证，发现该凭证自动完成以下过账分录：借记“库存商品-产成品（1405010000）”金额13.21，同时贷记“主营业务成本（6401000000）”金额13.21。通过对比系统后台配置（事务代码OBYC查看BSX与GBB/BVA配置），确认该自动分录的借贷方向、会计科目及金额与预设逻辑完全一致。执行过程中，未发现任何人工干预痕迹，系统依据物料主数据及移动类型自动触发了上述过账。
-结论：  
-经核对，该自动化过账行为符合系统预设的自动过账配置逻辑，测试结果满意。
-[注：以上内容由 DeepSeek AI (deepseek-chat) 辅助生成，请审计人员结合实际IPE进行复核]</t>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>性质 / Nature</t>
         </is>
@@ -1340,7 +2801,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>类型 / Type</t>
         </is>
@@ -1352,34 +2813,34 @@
       </c>
     </row>
     <row r="26">
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>二、测试样本明细 (TOE)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>凭证号</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
@@ -1388,264 +2849,100 @@
     <row r="28">
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>4900019620</t>
+          <t>7000001</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>1405010000</t>
+          <t>500101</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>库存商品-产成品</t>
+          <t>生产成本-基本生产</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>13.21</v>
+        <v>20000</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>4900019620</t>
+          <t>7000002</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>1405010000</t>
+          <t>140501</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>库存商品-产成品</t>
+          <t>库存商品-成品</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>54.18</v>
+        <v>45000</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="D2:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>设计和执行(D&amp;I)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>了解流程控制活动 / Understand the process control activities</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>控制 / Control</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ITAC_GEN</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>产成品差异</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>流程风险点 / PRP ID</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>流程风险点 / PRP(s)</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>重大错报风险 / RMM</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>信息 / Information</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>该流程控制活动如何应对流程风险点(PRP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>PRP_01</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>一、设计有效性测试 (TOD)
-经测试，在SAP S/4HANA系统中，当产成品差异过账时，系统依据后台配置表OBYC（科目确定）及对应的事务码（Transaction Key）及评估类（Valuation Class），通过汇总差异类移动类型对应的物料成本差异，自动确定会计科目。具体而言，系统预设的自动结转逻辑为：借记“库存商品-产成品”科目（科目号1405010000），以反映产成品标准成本与实际成本之间的差异对存货价值的调整；同时，贷记“主营业务成本”科目（科目号6401000000），以同步结转该差异至当期损益。该借贷对应关系由系统配置中的差异科目确定规则（如交易码PRD）自动驱动，无需人工干预。
-二、执行有效性测试 (TOE)
-在本次测试中，选取2026年1月8日产生的产成品差异会计凭证（凭证号4900019620）作为样本。经核对，该凭证记录为：借记“库存商品-产成品”科目（科目号1405010000），金额13.21；贷记“主营业务成本”科目（科目号6401000000），金额13.21。测试人员通过SAP事务码FB03查看该凭证的明细行项目，并比对后台配置表OBYC中相应交易码（如PRD）与评估类组合的科目映射，确认系统自动生成的借方与贷方科目、金额及方向，与预设的自动过账逻辑完全一致。
-结论：
-经核对，该自动化过账行为符合系统预设的自动过账配置逻辑，测试结果满意。
-[注：以上内容由 DeepSeek AI (deepseek-chat) 辅助生成，请审计人员结合实际IPE进行复核]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>性质 / Nature</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>自动化【AUTOMATED】</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>类型 / Type</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>预防性【PREVENTIVE】</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>二、测试样本明细 (TOE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>凭证号</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>科目</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>4900019620</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>1405010000</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-产成品</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>4900019620</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>1405010000</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-产成品</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>7000003</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>140502</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>库存商品-产成品差异</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>7000004</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
         </is>
       </c>
     </row>

--- a/data/WorkingPaper_Final.xlsx
+++ b/data/WorkingPaper_Final.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计总览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法论与较佳实践 (WGLL)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完工入库" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售发货" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售成本结转" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生产领料" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购收货" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购入账" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购收货" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生产领料" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完工入库" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采购入账" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售发货" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售成本结转" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工单差异" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产成品差异" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>销售入账</t>
+          <t>采购收货</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2,260,000.00</t>
+          <t>2,300,000.00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>未匹配到样本</t>
+          <t>通过 (4个样本)</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>完工入库</t>
+          <t>生产领料</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1,730,000.00</t>
+          <t>2,300,000.00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>通过 (6个样本)</t>
+          <t>通过 (4个样本)</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售发货</t>
+          <t>销售入账</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1,630,000.00</t>
+          <t>2,260,000.00</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>通过 (5个样本)</t>
+          <t>未匹配到样本</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>销售成本结转</t>
+          <t>完工入库</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1,630,000.00</t>
+          <t>1,405,000.00</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>生产领料</t>
+          <t>采购入账</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1,515,000.00</t>
+          <t>1,220,000.00</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>通过 (4个样本)</t>
+          <t>通过 (1个样本)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>采购收货</t>
+          <t>收款核销</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1,510,000.00</t>
+          <t>1,130,000.00</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>通过 (2个样本)</t>
+          <t>未匹配到样本</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>采购入账</t>
+          <t>销售发货</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1,220,000.00</t>
+          <t>820,000.00</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>通过 (1个样本)</t>
+          <t>通过 (3个样本)</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>收款核销</t>
+          <t>销售成本结转</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1,130,000.00</t>
+          <t>800,000.00</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>未匹配到样本</t>
+          <t>通过 (3个样本)</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>910,000.00</t>
+          <t>15,000.00</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>通过 (4个样本)</t>
+          <t>通过 (1个样本)</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>830,000.00</t>
+          <t>5,000.00</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>通过 (5个样本)</t>
+          <t>通过 (2个样本)</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D2:H32"/>
+  <dimension ref="D2:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -963,32 +963,32 @@
     <row r="28">
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>1000001</t>
+          <t>7000003</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>640101</t>
+          <t>140502</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>主营业务成本-产品A</t>
+          <t>库存商品-产成品差异</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>50000</v>
+        <v>500</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1000003</t>
+          <t>7000004</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1002,84 +1002,9 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45000</v>
+        <v>300</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>7000002</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>140501</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-成品</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>7000003</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>140502</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-产成品差异</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>7000004</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>640101</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>主营业务成本-产品A</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>2025-07-04</t>
         </is>
@@ -1159,7 +1084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D2:H33"/>
+  <dimension ref="D2:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1198,7 +1123,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>完工入库</t>
+          <t>采购收货</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1167,7 @@
         <is>
           <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
 [自动回退至模拟数据]:
-（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+在审计期间内，系统根据 OBYC 中 WRX (GR/IR) 的自动过账配置，在采购收货环节自动生成了凭证号为 5000001 的会计凭证。该凭证记录金额 30,000.00，借记原材料 (140301)，贷记应付暂估 (220202)。经核对，该自动化过账行为符合 system 配置要求，穿行测试结果满意。
 [注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
         </is>
       </c>
@@ -1333,25 +1258,25 @@
     <row r="29">
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1000003</t>
+          <t>5000001</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>640101</t>
+          <t>140301</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>主营业务成本-产品A</t>
+          <t>原材料-钢材</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-06-01</t>
         </is>
       </c>
     </row>
@@ -1402,56 +1327,6 @@
       <c r="H31" s="3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>7000003</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>140502</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-产成品差异</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>7000004</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>640101</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>主营业务成本-产品A</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D2:H32"/>
+  <dimension ref="D2:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1509,7 +1384,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>销售发货</t>
+          <t>生产领料</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1428,7 @@
         <is>
           <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
 [自动回退至模拟数据]:
-在审计期间内，系统根据 T030 表中 GBB-VAX 的自动过账配置，在销售发货环节自动生成了凭证号为 1000001 的会计日记账。该凭证金额为 50,000.00，借记主营业务成本 (640101)，贷记库存商品 (140501)。经审计核对，该样本的财务记录与系统预设的自动结转成本逻辑完全一致，控制设计有效并得到执行。
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
 [注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
         </is>
       </c>
@@ -1644,100 +1519,75 @@
     <row r="29">
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1000003</t>
+          <t>5000001</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>640101</t>
+          <t>140301</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>主营业务成本-产品A</t>
+          <t>原材料-钢材</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-06-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7000002</t>
+          <t>7000001</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>140501</t>
+          <t>500101</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>库存商品-成品</t>
+          <t>生产成本-基本生产</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45000</v>
+        <v>20000</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7000003</t>
+          <t>7000002</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>140502</t>
+          <t>140501</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>库存商品-产成品差异</t>
+          <t>库存商品-成品</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>500</v>
+        <v>45000</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>7000004</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>640101</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>主营业务成本-产品A</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
+          <t>2025-07-02</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1645,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>销售成本结转</t>
+          <t>完工入库</t>
         </is>
       </c>
     </row>
@@ -1930,100 +1780,100 @@
     <row r="29">
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>1000003</t>
+          <t>5000001</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>640101</t>
+          <t>140301</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>主营业务成本-产品A</t>
+          <t>原材料-钢材</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-06-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7000002</t>
+          <t>7000001</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>140501</t>
+          <t>500101</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>库存商品-成品</t>
+          <t>生产成本-基本生产</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45000</v>
+        <v>20000</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7000003</t>
+          <t>7000002</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>140502</t>
+          <t>140501</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>库存商品-产成品差异</t>
+          <t>库存商品-成品</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>500</v>
+        <v>45000</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7000004</t>
+          <t>7000003</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>640101</t>
+          <t>140502</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>主营业务成本-产品A</t>
+          <t>库存商品-产成品差异</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
@@ -2037,478 +1887,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="D2:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>设计和执行(D&amp;I)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>了解流程控制活动 / Understand the process control activities</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>控制 / Control</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ITAC_GEN</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>生产领料</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>流程风险点 / PRP ID</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>流程风险点 / PRP(s)</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>重大错报风险 / RMM</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>信息 / Information</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>该流程控制活动如何应对流程风险点(PRP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>PRP_01</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
-[自动回退至模拟数据]:
-（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
-[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>性质 / Nature</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>自动化【AUTOMATED】</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>类型 / Type</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>预防性【PREVENTIVE】</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>二、测试样本明细 (TOE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>凭证号</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>科目</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>5000001</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>原材料-钢材</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>7000001</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>500101</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>生产成本-基本生产</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>7000002</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>140501</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-成品</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>7000003</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>140502</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>库存商品-产成品差异</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="D2:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>设计和执行(D&amp;I)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>了解流程控制活动 / Understand the process control activities</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>控制 / Control</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ITAC_GEN</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>采购收货</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>流程风险点 / PRP ID</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>流程风险点 / PRP(s)</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>重大错报风险 / RMM</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>信息 / Information</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>该流程控制活动如何应对流程风险点(PRP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>PRP_01</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
-[自动回退至模拟数据]:
-在审计期间内，系统根据 OBYC 中 WRX (GR/IR) 的自动过账配置，在采购收货环节自动生成了凭证号为 5000001 的会计凭证。该凭证记录金额 30,000.00，借记原材料 (140301)，贷记应付暂估 (220202)。经核对，该自动化过账行为符合 system 配置要求，穿行测试结果满意。
-[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>性质 / Nature</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>自动化【AUTOMATED】</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>类型 / Type</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>预防性【PREVENTIVE】</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>二、测试样本明细 (TOE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>凭证号</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>科目</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>5000001</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>140301</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>原材料-钢材</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>7000001</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>500101</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>生产成本-基本生产</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2694,13 +2072,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D2:H31"/>
+  <dimension ref="D2:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2739,7 +2117,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>工单差异</t>
+          <t>销售发货</t>
         </is>
       </c>
     </row>
@@ -2783,6 +2161,242 @@
         <is>
           <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
 [自动回退至模拟数据]:
+在审计期间内，系统根据 T030 表中 GBB-VAX 的自动过账配置，在销售发货环节自动生成了凭证号为 1000001 的会计日记账。该凭证金额为 50,000.00，借记主营业务成本 (640101)，贷记库存商品 (140501)。经审计核对，该样本的财务记录与系统预设的自动结转成本逻辑完全一致，控制设计有效并得到执行。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>性质 / Nature</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>自动化【AUTOMATED】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>类型 / Type</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>预防性【PREVENTIVE】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二、测试样本明细 (TOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1000003</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>7000004</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="D2:H30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>设计和执行(D&amp;I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>了解流程控制活动 / Understand the process control activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>控制 / Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ITAC_GEN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>销售成本结转</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP ID</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP(s)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>重大错报风险 / RMM</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>信息 / Information</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>该流程控制活动如何应对流程风险点(PRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>PRP_01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
 （AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
 [注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
         </is>
@@ -2849,42 +2463,42 @@
     <row r="28">
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7000001</t>
+          <t>1000001</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>500101</t>
+          <t>640101</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>生产成本-基本生产</t>
+          <t>主营业务成本-产品A</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7000002</t>
+          <t>1000003</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>140501</t>
+          <t>640101</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>库存商品-成品</t>
+          <t>主营业务成本-产品A</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
@@ -2892,57 +2506,218 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="3" t="inlineStr">
         <is>
+          <t>7000004</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>640101</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>主营业务成本-产品A</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="D2:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>设计和执行(D&amp;I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>了解流程控制活动 / Understand the process control activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>控制 / Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ITAC_GEN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>工单差异</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP ID</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>流程风险点 / PRP(s)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>重大错报风险 / RMM</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>信息 / Information</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>该流程控制活动如何应对流程风险点(PRP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>PRP_01</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>DeepSeek AI (deepseek-chat) 生成失败: Error code: 401 - {'error': {'message': 'Authentication Fails, Your api key: ****-use is invalid', 'type': 'authentication_error', 'param': None, 'code': 'invalid_request_error'}}
+[自动回退至模拟数据]:
+（AI 模拟生成）系统已根据预设配置自动生成了样本凭证，借贷方向与金额均符合审计预期逻辑。
+[注：以上内容由 审计AI模拟引擎 生成，仅用于演示及功能验证]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>性质 / Nature</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>自动化【AUTOMATED】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>类型 / Type</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>预防性【PREVENTIVE】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>二、测试样本明细 (TOE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="3" t="inlineStr">
+        <is>
           <t>7000003</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>140502</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>库存商品-产成品差异</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G28" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>7000004</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>640101</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>主营业务成本-产品A</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
         </is>
       </c>
     </row>
